--- a/tests/SafeOpenXml.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8e3ff69455704879"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R971115457c3140c4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R971115457c3140c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra196d59fc5324c6d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra196d59fc5324c6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd68d8006ca1946b7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd68d8006ca1946b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Reaa3cbeb4662415a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Reaa3cbeb4662415a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R321a601441854f37"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R321a601441854f37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re3f62712aebf4a5c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re3f62712aebf4a5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R558be2df090f462a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R558be2df090f462a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7981f940f8454fde"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7981f940f8454fde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R542f5d91fe4944d3"/>
   </x:sheets>
 </x:workbook>
 </file>
